--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487717_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487717_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3833</v>
+        <v>4.372</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2409</v>
+        <v>3.2023</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1424</v>
+        <v>1.1697</v>
       </c>
       <c r="G2" t="n">
         <v>2.581</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7097</v>
+        <v>0.279</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3201</v>
+        <v>-0.3587</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6377</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2343</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2332</v>
+        <v>2.023</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5993</v>
+        <v>3.4982</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3662</v>
+        <v>-1.4752</v>
       </c>
       <c r="G3" t="n">
         <v>0.6513</v>
@@ -688,13 +688,13 @@
         <v>0.194</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0863</v>
+        <v>0.8762</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7597</v>
+        <v>0.6586</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3266</v>
+        <v>0.2176</v>
       </c>
       <c r="V3" t="n">
         <v>1.2716</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7015</v>
+        <v>1.8165</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4552</v>
+        <v>4.5158</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7537</v>
+        <v>-2.6992</v>
       </c>
       <c r="G4" t="n">
         <v>2.385</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3762</v>
+        <v>0.4912</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2288</v>
+        <v>-0.1683</v>
       </c>
       <c r="U4" t="n">
-        <v>0.605</v>
+        <v>0.6595</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8358</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1198</v>
+        <v>-0.0058</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8354</v>
+        <v>0.2002</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9552</v>
+        <v>-0.206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7368</v>
+        <v>-0.206</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6261</v>
+        <v>-0.206</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1106</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7333</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1183</v>
+        <v>-0.206</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1071</v>
+        <v>-0.206</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0111</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6494</v>
+        <v>0.2002</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6684</v>
+        <v>0.2002</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0191</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.206</v>
+        <v>-0.2232</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.5957</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.206</v>
+        <v>-0.8189</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.206</v>
+        <v>0.7368</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.206</v>
+        <v>0.6261</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.1106</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.7333</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1218</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.206</v>
+        <v>-0.1183</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.206</v>
+        <v>-0.1071</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.0111</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4287</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4837</v>
+        <v>-0.3291</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1392</v>
+        <v>-0.0392</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3445</v>
+        <v>-0.29</v>
       </c>
       <c r="G7" t="n">
         <v>-0.593</v>
@@ -1000,13 +1000,13 @@
         <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4729</v>
+        <v>-0.3182</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>-0.2027</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.17</v>
+        <v>-0.1155</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6496</v>
+        <v>-1.0497</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2378</v>
+        <v>-1.1289</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5883</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4871</v>
+        <v>0.1476</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6039</v>
+        <v>0.8494</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1168</v>
+        <v>-0.7018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5936</v>
+        <v>2.1068</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2183</v>
+        <v>0.7621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8119</v>
+        <v>1.3447</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0808</v>
+        <v>-1.9592</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3856</v>
+        <v>0.0873</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6952</v>
+        <v>-2.0466</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9403</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0747</v>
+        <v>-3.1045</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>3.0018</v>
+        <v>0.443</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3492</v>
+        <v>-0.1313</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6526</v>
+        <v>0.5743</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1179</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8117</v>
+        <v>-1.2235</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1142</v>
+        <v>-1.117</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9259</v>
+        <v>-0.1065</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1471</v>
+        <v>-2.1071</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1961</v>
+        <v>-1.6255</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.951</v>
+        <v>-0.4816</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0824</v>
+        <v>-1.7944</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0824</v>
+        <v>-1.1905</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6039</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2294</v>
+        <v>-0.3127</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2785</v>
+        <v>-0.435</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.951</v>
+        <v>0.1223</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9771</v>
+        <v>1.0492</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0318</v>
+        <v>0.3953</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0547</v>
+        <v>0.6539</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2239</v>
+        <v>-0.9418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2239</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4561</v>
+        <v>-1.4852</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5899</v>
+        <v>0.4135</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1338</v>
+        <v>-1.8987</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1476</v>
+        <v>-1.1471</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8494</v>
+        <v>-0.1961</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7018</v>
+        <v>-0.951</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1068</v>
+        <v>0.0824</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7621</v>
+        <v>0.0824</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3447</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9592</v>
+        <v>-1.2294</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0873</v>
+        <v>-0.2785</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0466</v>
+        <v>-0.951</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0366</v>
+        <v>0.3037</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.3311</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6288</v>
+        <v>-0.0275</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4426</v>
+        <v>-2.3169</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.118</v>
+        <v>-2.2783</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3246</v>
+        <v>-0.0386</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1071</v>
+        <v>-0.4871</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6255</v>
+        <v>-0.6039</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4816</v>
+        <v>0.1168</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7944</v>
+        <v>0.5936</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1905</v>
+        <v>-0.2183</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6039</v>
+        <v>0.8119</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3127</v>
+        <v>-1.0808</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.435</v>
+        <v>-0.3856</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1223</v>
+        <v>-0.6952</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7761</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.0747</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7761</v>
+        <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1698</v>
+        <v>1.3344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>0.3087</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4359</v>
+        <v>1.0257</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9418</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>-2.1179</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9488</v>
+        <v>-6.0756</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3219</v>
+        <v>-4.7213</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6268</v>
+        <v>-1.3543</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0634</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7391</v>
+        <v>0.134</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.2956</v>
       </c>
       <c r="U12" t="n">
-        <v>0.157</v>
+        <v>0.4296</v>
       </c>
       <c r="V12" t="n">
         <v>-1.788</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8003</v>
+        <v>-4.497499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8382</v>
+        <v>3.140999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.6384</v>
+        <v>-7.6385</v>
       </c>
       <c r="G13" t="n">
         <v>-1.102</v>
@@ -1456,10 +1456,10 @@
         <v>-1.6808</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.926099999999998</v>
+        <v>-8.9261</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9701000000000003</v>
+        <v>-0.9701000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.6121</v>
@@ -1468,16 +1468,16 @@
         <v>11.642</v>
       </c>
       <c r="S13" t="n">
-        <v>5.035899999999999</v>
+        <v>5.3386</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8633000000000001</v>
+        <v>1.166</v>
       </c>
       <c r="U13" t="n">
         <v>4.1725</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.7642</v>
+        <v>-7.764200000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.082100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9789</v>
+        <v>5.8855</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9391</v>
+        <v>5.7317</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9602000000000001</v>
+        <v>0.1538</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4712</v>
+        <v>0.3826</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6772</v>
+        <v>-3.5781</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1484</v>
+        <v>3.9607</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1371</v>
+        <v>2.3884</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2688</v>
+        <v>-2.0061</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1317</v>
+        <v>4.3945</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6083</v>
+        <v>-2.0058</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5916</v>
+        <v>-1.572</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0167</v>
+        <v>-0.4338</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4367</v>
+        <v>-0.6732</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1171</v>
+        <v>-0.8925</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3197</v>
+        <v>0.2193</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7895</v>
+        <v>4.2358</v>
       </c>
       <c r="W14" t="n">
-        <v>7.6253</v>
+        <v>4.2358</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4612</v>
+        <v>5.0419</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6316</v>
+        <v>6.1384</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1704</v>
+        <v>-1.0965</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3826</v>
+        <v>-0.4712</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.5781</v>
+        <v>0.6772</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9607</v>
+        <v>-1.1484</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3884</v>
+        <v>0.1371</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.0061</v>
+        <v>1.2688</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3945</v>
+        <v>-1.1317</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0058</v>
+        <v>-0.6083</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.572</v>
+        <v>-0.5916</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4338</v>
+        <v>-0.0167</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9403</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0976</v>
+        <v>0.4997</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9926</v>
+        <v>0.3163</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1049</v>
+        <v>0.1834</v>
       </c>
       <c r="V15" t="n">
-        <v>4.2358</v>
+        <v>5.7895</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2358</v>
+        <v>7.6253</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9288</v>
+        <v>2.089</v>
       </c>
       <c r="E16" t="n">
-        <v>1.163</v>
+        <v>1.935</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7658</v>
+        <v>0.154</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2023</v>
+        <v>0.7498</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1812</v>
+        <v>-0.3007</v>
       </c>
       <c r="I16" t="n">
-        <v>1.021</v>
+        <v>1.0505</v>
       </c>
       <c r="J16" t="n">
-        <v>1.744</v>
+        <v>1.764</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1122</v>
+        <v>0.4243</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6318</v>
+        <v>1.3397</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5417</v>
+        <v>-1.0142</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.931</v>
+        <v>-0.725</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3893</v>
+        <v>-0.2892</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6317</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.581</v>
+        <v>-0.3931</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0507</v>
+        <v>-0.1497</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4011</v>
+        <v>1.5929</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7348</v>
+        <v>1.2631</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3338</v>
+        <v>0.3298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7498</v>
+        <v>1.2023</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3007</v>
+        <v>0.1812</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0505</v>
+        <v>1.021</v>
       </c>
       <c r="J17" t="n">
-        <v>1.764</v>
+        <v>1.744</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4243</v>
+        <v>1.1122</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3397</v>
+        <v>0.6318</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0142</v>
+        <v>-0.5417</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.725</v>
+        <v>-0.931</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2892</v>
+        <v>0.3893</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2308</v>
+        <v>-0.9676</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5933</v>
+        <v>-0.4809</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6375</v>
+        <v>-0.4867</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4325</v>
+        <v>0.9114</v>
       </c>
       <c r="E18" t="n">
-        <v>1.423</v>
+        <v>1.5231</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.6117</v>
       </c>
       <c r="G18" t="n">
         <v>0.4403</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.1214</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.4327</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0675</v>
+        <v>0.3113</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3776</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3144</v>
+        <v>0.4234</v>
       </c>
       <c r="E19" t="n">
         <v>0.4018</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="G19" t="n">
         <v>1.5545</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0121</v>
+        <v>0.1211</v>
       </c>
       <c r="T19" t="n">
         <v>0.07290000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2917</v>
+        <v>-0.1587</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6293</v>
+        <v>-0.9296</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3376</v>
+        <v>0.7709</v>
       </c>
       <c r="G21" t="n">
         <v>0.4312</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3154</v>
+        <v>-1.1824</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4105</v>
+        <v>-0.7108</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9049</v>
+        <v>-0.4716</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3776</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6936</v>
+        <v>-0.7481</v>
       </c>
       <c r="E22" t="n">
         <v>0.1538</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8474</v>
+        <v>-0.9019</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0321</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1092</v>
+        <v>-0.1637</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U22" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V22" t="n">
         <v>1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.671</v>
+        <v>-2.4007</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2696</v>
+        <v>-2.9693</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5986</v>
+        <v>0.5686</v>
       </c>
       <c r="G23" t="n">
         <v>1.0392</v>
@@ -2248,13 +2248,13 @@
         <v>2.3284</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8862</v>
+        <v>-0.616</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7504</v>
+        <v>-0.4501</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1359</v>
+        <v>-0.166</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2716</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.582</v>
+        <v>-3.591</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6346</v>
+        <v>-2.5345</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9474</v>
+        <v>-1.0564</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6934</v>
@@ -2326,13 +2326,13 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9946</v>
+        <v>-1.0035</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2678</v>
+        <v>-0.3768</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6118</v>
+        <v>-3.7114</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2752</v>
+        <v>-3.075</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3366</v>
+        <v>-0.6364</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6347</v>
@@ -2404,13 +2404,13 @@
         <v>0.7761</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3811</v>
+        <v>0.2815</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3326</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9139</v>
+        <v>0.6141</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2239</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.800300000000002</v>
+        <v>5.467699999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>7.638399999999999</v>
+        <v>7.638500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.8382</v>
+        <v>-2.1708</v>
       </c>
       <c r="G26" t="n">
         <v>1.102</v>
@@ -2482,13 +2482,13 @@
         <v>12.6121</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.0359</v>
+        <v>-4.3683</v>
       </c>
       <c r="T26" t="n">
         <v>-4.1725</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8634000000000001</v>
+        <v>-0.1960000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>7.764200000000002</v>
